--- a/Entregables/Matriz-Interesados-14-09.xlsx
+++ b/Entregables/Matriz-Interesados-14-09.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://frbautneduar-my.sharepoint.com/personal/jomansilla_frba_utn_edu_ar/Documents/04-Cuarto-Año-2026/Administracion-De-Sistemas-De-Información/TPA/Entregables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="11_F25DC773A252ABDACC1048BDA95E51B25BDE58E7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02B41A04-B023-435B-9AD6-31739583ECA5}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="11_F25DC773A252ABDACC1048BDA95E51B25BDE58E7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3DFA2F4-EF01-4EB2-BCD0-CA18D78E60DF}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="492" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="480" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -391,12 +391,6 @@
     <t>Matriz de Identificación de los Interesados del Proyecto</t>
   </si>
   <si>
-    <t>Plataforma SaaS Institucional para Gestión de Becas Académicas  |  Versión 1.0  |  02/07/2026</t>
-  </si>
-  <si>
-    <t>BECA360 — Registro de los Interesados del Proyecto</t>
-  </si>
-  <si>
     <t>Producto escalable y rentable; ingresos sostenidos por suscripciones institucionales</t>
   </si>
   <si>
@@ -413,6 +407,12 @@
   </si>
   <si>
     <t>Pendiente</t>
+  </si>
+  <si>
+    <t>“Desarrollo e implementación de la plataforma Integral para la Gestión y Administración de Becas Académicas (Beca360)”</t>
+  </si>
+  <si>
+    <t>Registro de los Interesados del Proyecto</t>
   </si>
 </sst>
 </file>
@@ -449,12 +449,14 @@
       <sz val="8"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -517,7 +519,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -537,29 +539,32 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -577,10 +582,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -847,58 +848,58 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5546875" customWidth="1"/>
-    <col min="2" max="2" width="22.5546875" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="16.5546875" customWidth="1"/>
-    <col min="5" max="5" width="33.33203125" customWidth="1"/>
-    <col min="7" max="7" width="46.109375" customWidth="1"/>
-    <col min="8" max="8" width="17.21875" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" customWidth="1"/>
+    <col min="2" max="2" width="22.5703125" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" customWidth="1"/>
+    <col min="5" max="5" width="33.28515625" customWidth="1"/>
+    <col min="7" max="7" width="46.140625" customWidth="1"/>
+    <col min="8" max="8" width="17.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-    </row>
-    <row r="4" spans="1:9" ht="24" x14ac:dyDescent="0.3">
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+    </row>
+    <row r="4" spans="1:9" ht="24" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>92</v>
       </c>
@@ -921,13 +922,13 @@
         <v>86</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>84</v>
       </c>
@@ -938,25 +939,25 @@
         <v>82</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>29</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
@@ -967,7 +968,7 @@
         <v>80</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>79</v>
@@ -976,16 +977,16 @@
         <v>29</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
@@ -996,7 +997,7 @@
         <v>77</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>76</v>
@@ -1008,13 +1009,13 @@
         <v>75</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>23</v>
       </c>
@@ -1025,7 +1026,7 @@
         <v>73</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>72</v>
@@ -1037,13 +1038,13 @@
         <v>71</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>70</v>
       </c>
@@ -1054,7 +1055,7 @@
         <v>68</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>67</v>
@@ -1066,13 +1067,13 @@
         <v>66</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>64</v>
       </c>
@@ -1083,7 +1084,7 @@
         <v>62</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>61</v>
@@ -1095,13 +1096,13 @@
         <v>60</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -1112,7 +1113,7 @@
         <v>58</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>57</v>
@@ -1124,13 +1125,13 @@
         <v>56</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>55</v>
       </c>
@@ -1141,7 +1142,7 @@
         <v>53</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>52</v>
@@ -1153,13 +1154,13 @@
         <v>51</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>49</v>
       </c>
@@ -1170,7 +1171,7 @@
         <v>47</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>46</v>
@@ -1182,13 +1183,13 @@
         <v>45</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>3</v>
       </c>
@@ -1199,7 +1200,7 @@
         <v>42</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>41</v>
@@ -1211,26 +1212,26 @@
         <v>40</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>37</v>
       </c>
@@ -1240,219 +1241,207 @@
       <c r="C17" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
       <c r="F17" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-    </row>
-    <row r="18" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+    </row>
+    <row r="18" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="12" t="s">
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-    </row>
-    <row r="19" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+    </row>
+    <row r="19" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="7" t="s">
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-    </row>
-    <row r="20" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+    </row>
+    <row r="20" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="12" t="s">
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-    </row>
-    <row r="21" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+    </row>
+    <row r="21" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="7" t="s">
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-    </row>
-    <row r="22" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+    </row>
+    <row r="22" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="12" t="s">
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-    </row>
-    <row r="23" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+    </row>
+    <row r="23" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="7" t="s">
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-    </row>
-    <row r="24" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+    </row>
+    <row r="24" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="12" t="s">
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-    </row>
-    <row r="25" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+    </row>
+    <row r="25" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="7" t="s">
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-    </row>
-    <row r="26" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+    </row>
+    <row r="26" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="12" t="s">
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-    </row>
-    <row r="27" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+    </row>
+    <row r="27" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="7" t="s">
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="F17:I17"/>
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="A16:I16"/>
     <mergeCell ref="C23:E23"/>
@@ -1467,6 +1456,18 @@
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="C25:E25"/>
     <mergeCell ref="F24:I24"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="F17:I17"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="149" orientation="landscape" r:id="rId1"/>
